--- a/ZAC_zzx/results/fourway/四方法_四指标_双数据集.xlsx
+++ b/ZAC_zzx/results/fourway/四方法_四指标_双数据集.xlsx
@@ -621,7 +621,7 @@
         <v>0.8456050000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>3.923</v>
+        <v>0.004</v>
       </c>
       <c r="O3" t="n">
         <v>27</v>
@@ -691,7 +691,7 @@
         <v>0.77949</v>
       </c>
       <c r="N4" t="n">
-        <v>5.353</v>
+        <v>0.005</v>
       </c>
       <c r="O4" t="n">
         <v>36</v>
@@ -761,7 +761,7 @@
         <v>0.742319</v>
       </c>
       <c r="N5" t="n">
-        <v>5.594</v>
+        <v>0.006</v>
       </c>
       <c r="O5" t="n">
         <v>35</v>
@@ -831,7 +831,7 @@
         <v>0.355945</v>
       </c>
       <c r="N6" t="n">
-        <v>12.054</v>
+        <v>0.012</v>
       </c>
       <c r="O6" t="n">
         <v>71</v>
@@ -901,7 +901,7 @@
         <v>0.737967</v>
       </c>
       <c r="N7" t="n">
-        <v>6.611</v>
+        <v>0.007</v>
       </c>
       <c r="O7" t="n">
         <v>42</v>
@@ -971,7 +971,7 @@
         <v>0.552795</v>
       </c>
       <c r="N8" t="n">
-        <v>10.883</v>
+        <v>0.011</v>
       </c>
       <c r="O8" t="n">
         <v>67</v>
@@ -1041,7 +1041,7 @@
         <v>0.723774</v>
       </c>
       <c r="N9" t="n">
-        <v>6.852</v>
+        <v>0.007</v>
       </c>
       <c r="O9" t="n">
         <v>43</v>
@@ -1111,7 +1111,7 @@
         <v>0.483449</v>
       </c>
       <c r="N10" t="n">
-        <v>12.219</v>
+        <v>0.012</v>
       </c>
       <c r="O10" t="n">
         <v>77</v>
@@ -1181,7 +1181,7 @@
         <v>0.122912</v>
       </c>
       <c r="N11" t="n">
-        <v>24.602</v>
+        <v>0.025</v>
       </c>
       <c r="O11" t="n">
         <v>154</v>
@@ -1251,7 +1251,7 @@
         <v>0.373607</v>
       </c>
       <c r="N12" t="n">
-        <v>482.645</v>
+        <v>0.483</v>
       </c>
       <c r="O12" t="n">
         <v>24</v>
@@ -1321,7 +1321,7 @@
         <v>0.045217</v>
       </c>
       <c r="N13" t="n">
-        <v>421.114</v>
+        <v>0.421</v>
       </c>
       <c r="O13" t="n">
         <v>29</v>
@@ -1391,7 +1391,7 @@
         <v>0.216848</v>
       </c>
       <c r="N14" t="n">
-        <v>62.085</v>
+        <v>0.062</v>
       </c>
       <c r="O14" t="n">
         <v>95</v>
@@ -1461,7 +1461,7 @@
         <v>0.627989</v>
       </c>
       <c r="N15" t="n">
-        <v>8.311999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="O15" t="n">
         <v>49</v>
@@ -1531,7 +1531,7 @@
         <v>0.069442</v>
       </c>
       <c r="N16" t="n">
-        <v>31.357</v>
+        <v>0.031</v>
       </c>
       <c r="O16" t="n">
         <v>187</v>
@@ -1601,7 +1601,7 @@
         <v>0.002485</v>
       </c>
       <c r="N17" t="n">
-        <v>64.22</v>
+        <v>0.064</v>
       </c>
       <c r="O17" t="n">
         <v>407</v>
@@ -1671,7 +1671,7 @@
         <v>0.427854</v>
       </c>
       <c r="N18" t="n">
-        <v>14.125</v>
+        <v>0.014</v>
       </c>
       <c r="O18" t="n">
         <v>69</v>
@@ -1741,7 +1741,7 @@
         <v>0.319186</v>
       </c>
       <c r="N19" t="n">
-        <v>26.794</v>
+        <v>0.027</v>
       </c>
       <c r="O19" t="n">
         <v>73</v>
@@ -1811,7 +1811,7 @@
         <v>0.433833</v>
       </c>
       <c r="N20" t="n">
-        <v>11.445</v>
+        <v>0.011</v>
       </c>
       <c r="O20" t="n">
         <v>79</v>
@@ -2003,7 +2003,7 @@
       <c r="L25" s="3" t="inlineStr"/>
       <c r="M25" s="3" t="inlineStr"/>
       <c r="N25" s="3" t="n">
-        <v>1210.2</v>
+        <v>1.2</v>
       </c>
       <c r="O25" s="3" t="inlineStr"/>
       <c r="P25" s="3" t="inlineStr"/>
